--- a/data/nuevos_clientes.xlsx
+++ b/data/nuevos_clientes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C116"/>
+  <dimension ref="A1:C122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -892,7 +892,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="37">
@@ -1932,7 +1932,85 @@
         </is>
       </c>
       <c r="C116" t="n">
-        <v>2</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>115</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>116</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>117</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>118</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>119</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>120</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>8</v>
       </c>
     </row>
   </sheetData>

--- a/data/nuevos_clientes.xlsx
+++ b/data/nuevos_clientes.xlsx
@@ -2010,7 +2010,7 @@
         </is>
       </c>
       <c r="C122" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/data/nuevos_clientes.xlsx
+++ b/data/nuevos_clientes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C122"/>
+  <dimension ref="A1:D202"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,6 +436,11 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>Unidad de Negocios</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>ClientesNuevos</t>
         </is>
       </c>
@@ -449,7 +454,12 @@
           <t>2016-01</t>
         </is>
       </c>
-      <c r="C2" t="n">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -462,7 +472,12 @@
           <t>2016-04</t>
         </is>
       </c>
-      <c r="C3" t="n">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
         <v>6</v>
       </c>
     </row>
@@ -475,8 +490,13 @@
           <t>2016-05</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>5</v>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
@@ -485,11 +505,16 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2016-07</t>
-        </is>
-      </c>
-      <c r="C5" t="n">
-        <v>5</v>
+          <t>2016-05</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -498,11 +523,16 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2016-08</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>4</v>
+          <t>2016-07</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -511,11 +541,16 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2016-09</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>5</v>
+          <t>2016-07</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -524,11 +559,16 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2016-10</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>5</v>
+          <t>2016-08</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -537,11 +577,16 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2016-11</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>6</v>
+          <t>2016-08</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -550,11 +595,16 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2016-12</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>55</v>
+          <t>2016-09</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -563,11 +613,16 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2017-01</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>71</v>
+          <t>2016-09</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="12">
@@ -576,11 +631,16 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2017-02</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>28</v>
+          <t>2016-10</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -589,37 +649,52 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2017-03</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>37</v>
+          <t>2016-10</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2017-04</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>14</v>
+          <t>2016-11</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2017-05</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>28</v>
+          <t>2016-11</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="16">
@@ -628,11 +703,16 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2017-06</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>17</v>
+          <t>2016-12</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>39</v>
       </c>
     </row>
     <row r="17">
@@ -641,11 +721,16 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2017-07</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>15</v>
+          <t>2016-12</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="18">
@@ -654,11 +739,16 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2017-08</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>20</v>
+          <t>2016-12</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="19">
@@ -667,11 +757,16 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2017-09</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>15</v>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>46</v>
       </c>
     </row>
     <row r="20">
@@ -680,11 +775,16 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2017-10</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>10</v>
+          <t>2017-01</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="21">
@@ -693,11 +793,16 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2017-11</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>26</v>
+          <t>2017-02</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D21" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="22">
@@ -706,11 +811,16 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2017-12</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>14</v>
+          <t>2017-02</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="23">
@@ -719,11 +829,16 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2018-01</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>12</v>
+          <t>2017-03</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>37</v>
       </c>
     </row>
     <row r="24">
@@ -732,11 +847,16 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2018-02</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>18</v>
+          <t>2017-04</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="25">
@@ -745,37 +865,52 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2018-03</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>17</v>
+          <t>2017-04</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2018-04</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>8</v>
+          <t>2017-05</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2018-05</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>15</v>
+          <t>2017-05</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>26</v>
       </c>
     </row>
     <row r="28">
@@ -784,11 +919,16 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2018-06</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>14</v>
+          <t>2017-06</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="29">
@@ -797,11 +937,16 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2018-07</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>14</v>
+          <t>2017-06</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -810,11 +955,16 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2018-08</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>8</v>
+          <t>2017-07</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="31">
@@ -823,11 +973,16 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2018-09</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>12</v>
+          <t>2017-07</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="32">
@@ -836,11 +991,16 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2018-10</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>10</v>
+          <t>2017-08</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="33">
@@ -849,11 +1009,16 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2018-11</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>10</v>
+          <t>2017-08</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -862,11 +1027,16 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2018-12</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>9</v>
+          <t>2017-09</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="35">
@@ -875,11 +1045,16 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2019-01</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>5</v>
+          <t>2017-10</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="36">
@@ -888,11 +1063,16 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2019-02</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>11</v>
+          <t>2017-11</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="37">
@@ -901,37 +1081,52 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2019-03</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>6</v>
+          <t>2017-11</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2019-04</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>14</v>
+          <t>2017-12</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="n">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2019-05</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>12</v>
+          <t>2017-12</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="40">
@@ -940,11 +1135,16 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2019-06</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>13</v>
+          <t>2018-01</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="41">
@@ -953,11 +1153,16 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2019-07</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>13</v>
+          <t>2018-02</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>18</v>
       </c>
     </row>
     <row r="42">
@@ -966,11 +1171,16 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2019-08</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>10</v>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>16</v>
       </c>
     </row>
     <row r="43">
@@ -979,11 +1189,16 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2019-09</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>9</v>
+          <t>2018-03</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -992,11 +1207,16 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2019-10</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>7</v>
+          <t>2018-04</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="45">
@@ -1005,11 +1225,16 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2019-11</t>
-        </is>
-      </c>
-      <c r="C45" t="n">
-        <v>9</v>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="46">
@@ -1018,11 +1243,16 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2019-12</t>
-        </is>
-      </c>
-      <c r="C46" t="n">
-        <v>9</v>
+          <t>2018-05</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="47">
@@ -1031,11 +1261,16 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2020-01</t>
-        </is>
-      </c>
-      <c r="C47" t="n">
-        <v>7</v>
+          <t>2018-06</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="48">
@@ -1044,11 +1279,16 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>2020-02</t>
-        </is>
-      </c>
-      <c r="C48" t="n">
-        <v>6</v>
+          <t>2018-07</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>14</v>
       </c>
     </row>
     <row r="49">
@@ -1057,11 +1297,16 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>2020-03</t>
-        </is>
-      </c>
-      <c r="C49" t="n">
-        <v>11</v>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="50">
@@ -1070,36 +1315,51 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2020-04</t>
-        </is>
-      </c>
-      <c r="C50" t="n">
-        <v>6</v>
+          <t>2018-08</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2020-05</t>
-        </is>
-      </c>
-      <c r="C51" t="n">
-        <v>6</v>
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="n">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>2020-06</t>
-        </is>
-      </c>
-      <c r="C52" t="n">
+          <t>2018-09</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
         <v>10</v>
       </c>
     </row>
@@ -1109,11 +1369,16 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>2020-07</t>
-        </is>
-      </c>
-      <c r="C53" t="n">
-        <v>5</v>
+          <t>2018-10</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="54">
@@ -1122,11 +1387,16 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>2020-08</t>
-        </is>
-      </c>
-      <c r="C54" t="n">
-        <v>11</v>
+          <t>2018-11</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="55">
@@ -1135,11 +1405,16 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2020-09</t>
-        </is>
-      </c>
-      <c r="C55" t="n">
-        <v>11</v>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="56">
@@ -1148,11 +1423,16 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>2020-10</t>
-        </is>
-      </c>
-      <c r="C56" t="n">
-        <v>7</v>
+          <t>2018-12</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -1161,11 +1441,16 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2020-11</t>
-        </is>
-      </c>
-      <c r="C57" t="n">
-        <v>2</v>
+          <t>2019-01</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="58">
@@ -1174,11 +1459,16 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>2020-12</t>
-        </is>
-      </c>
-      <c r="C58" t="n">
-        <v>7</v>
+          <t>2019-02</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="59">
@@ -1187,11 +1477,16 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2021-01</t>
-        </is>
-      </c>
-      <c r="C59" t="n">
-        <v>7</v>
+          <t>2019-03</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="60">
@@ -1200,11 +1495,16 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>2021-02</t>
-        </is>
-      </c>
-      <c r="C60" t="n">
-        <v>8</v>
+          <t>2019-04</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="61">
@@ -1213,11 +1513,16 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2021-03</t>
-        </is>
-      </c>
-      <c r="C61" t="n">
-        <v>17</v>
+          <t>2019-04</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -1226,36 +1531,51 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2021-04</t>
-        </is>
-      </c>
-      <c r="C62" t="n">
-        <v>9</v>
+          <t>2019-05</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>12</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2021-05</t>
-        </is>
-      </c>
-      <c r="C63" t="n">
-        <v>4</v>
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>2021-06</t>
-        </is>
-      </c>
-      <c r="C64" t="n">
+          <t>2019-06</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
         <v>12</v>
       </c>
     </row>
@@ -1265,11 +1585,16 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>2021-07</t>
-        </is>
-      </c>
-      <c r="C65" t="n">
-        <v>20</v>
+          <t>2019-07</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>13</v>
       </c>
     </row>
     <row r="66">
@@ -1278,11 +1603,16 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>2021-08</t>
-        </is>
-      </c>
-      <c r="C66" t="n">
-        <v>17</v>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="67">
@@ -1291,11 +1621,16 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>2021-09</t>
-        </is>
-      </c>
-      <c r="C67" t="n">
-        <v>21</v>
+          <t>2019-08</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -1304,11 +1639,16 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2021-10</t>
-        </is>
-      </c>
-      <c r="C68" t="n">
-        <v>11</v>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="69">
@@ -1317,11 +1657,16 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2021-11</t>
-        </is>
-      </c>
-      <c r="C69" t="n">
-        <v>11</v>
+          <t>2019-09</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="70">
@@ -1330,11 +1675,16 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>2021-12</t>
-        </is>
-      </c>
-      <c r="C70" t="n">
-        <v>6</v>
+          <t>2019-10</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="71">
@@ -1343,11 +1693,16 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>2022-01</t>
-        </is>
-      </c>
-      <c r="C71" t="n">
-        <v>7</v>
+          <t>2019-11</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="72">
@@ -1356,10 +1711,15 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2022-02</t>
-        </is>
-      </c>
-      <c r="C72" t="n">
+          <t>2019-12</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1369,11 +1729,16 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>2022-03</t>
-        </is>
-      </c>
-      <c r="C73" t="n">
-        <v>8</v>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="74">
@@ -1382,11 +1747,16 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2022-04</t>
-        </is>
-      </c>
-      <c r="C74" t="n">
-        <v>11</v>
+          <t>2020-01</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="75">
@@ -1395,11 +1765,16 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2022-05</t>
-        </is>
-      </c>
-      <c r="C75" t="n">
-        <v>12</v>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="76">
@@ -1408,11 +1783,16 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2022-06</t>
-        </is>
-      </c>
-      <c r="C76" t="n">
-        <v>11</v>
+          <t>2020-02</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Otros</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="77">
@@ -1421,10 +1801,15 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2022-07</t>
-        </is>
-      </c>
-      <c r="C77" t="n">
+          <t>2020-03</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
         <v>11</v>
       </c>
     </row>
@@ -1434,11 +1819,16 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2022-08</t>
-        </is>
-      </c>
-      <c r="C78" t="n">
-        <v>10</v>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="79">
@@ -1447,11 +1837,16 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>2022-09</t>
-        </is>
-      </c>
-      <c r="C79" t="n">
-        <v>14</v>
+          <t>2020-04</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="80">
@@ -1460,11 +1855,16 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2022-10</t>
-        </is>
-      </c>
-      <c r="C80" t="n">
-        <v>11</v>
+          <t>2020-05</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="81">
@@ -1473,10 +1873,15 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2022-11</t>
-        </is>
-      </c>
-      <c r="C81" t="n">
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
         <v>8</v>
       </c>
     </row>
@@ -1486,11 +1891,16 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2022-12</t>
-        </is>
-      </c>
-      <c r="C82" t="n">
-        <v>6</v>
+          <t>2020-06</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="83">
@@ -1499,11 +1909,16 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2023-01</t>
-        </is>
-      </c>
-      <c r="C83" t="n">
-        <v>12</v>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="84">
@@ -1512,11 +1927,16 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2023-02</t>
-        </is>
-      </c>
-      <c r="C84" t="n">
-        <v>7</v>
+          <t>2020-07</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="85">
@@ -1525,11 +1945,16 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>2023-03</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>7</v>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="86">
@@ -1538,11 +1963,16 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>2023-04</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>12</v>
+          <t>2020-08</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="87">
@@ -1551,11 +1981,16 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>2023-05</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>8</v>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="88">
@@ -1564,37 +1999,52 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>2023-06</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>8</v>
+          <t>2020-09</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="n">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>2023-07</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>6</v>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>2023-08</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>7</v>
+          <t>2020-10</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="91">
@@ -1603,11 +2053,16 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>2023-09</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>9</v>
+          <t>2020-11</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="92">
@@ -1616,11 +2071,16 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>2023-10</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>6</v>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="93">
@@ -1629,11 +2089,16 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>2023-11</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>9</v>
+          <t>2020-12</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="94">
@@ -1642,11 +2107,16 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>2023-12</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>6</v>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="95">
@@ -1655,11 +2125,16 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>2024-01</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>8</v>
+          <t>2021-01</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="96">
@@ -1668,11 +2143,16 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>2024-02</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>8</v>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="97">
@@ -1681,11 +2161,16 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>2024-03</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>2</v>
+          <t>2021-02</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="98">
@@ -1694,11 +2179,16 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>2024-04</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>5</v>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>15</v>
       </c>
     </row>
     <row r="99">
@@ -1707,11 +2197,16 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>2024-05</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>9</v>
+          <t>2021-03</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D99" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="100">
@@ -1720,10 +2215,15 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>2024-06</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
+          <t>2021-04</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D100" t="n">
         <v>9</v>
       </c>
     </row>
@@ -1733,37 +2233,52 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>2024-07</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>8</v>
+          <t>2021-05</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D101" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>2024-08</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>9</v>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D102" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>2024-09</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>4</v>
+          <t>2021-06</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D103" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="104">
@@ -1772,11 +2287,16 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>2024-10</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>5</v>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D104" t="n">
+        <v>19</v>
       </c>
     </row>
     <row r="105">
@@ -1785,11 +2305,16 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>2024-11</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>8</v>
+          <t>2021-07</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D105" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="106">
@@ -1798,11 +2323,16 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>2024-12</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>8</v>
+          <t>2021-08</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D106" t="n">
+        <v>17</v>
       </c>
     </row>
     <row r="107">
@@ -1811,11 +2341,16 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>2025-01</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>4</v>
+          <t>2021-09</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D107" t="n">
+        <v>21</v>
       </c>
     </row>
     <row r="108">
@@ -1824,11 +2359,16 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>2025-02</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>8</v>
+          <t>2021-10</t>
+        </is>
+      </c>
+      <c r="C108" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D108" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="109">
@@ -1837,11 +2377,16 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>2025-03</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>7</v>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D109" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="110">
@@ -1850,11 +2395,16 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>2025-04</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>3</v>
+          <t>2021-11</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D110" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="111">
@@ -1863,11 +2413,16 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>2025-05</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>6</v>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D111" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="112">
@@ -1876,11 +2431,16 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>2025-06</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>10</v>
+          <t>2021-12</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D112" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="113">
@@ -1889,11 +2449,16 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>2025-07</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>10</v>
+          <t>2022-01</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D113" t="n">
+        <v>7</v>
       </c>
     </row>
     <row r="114">
@@ -1902,37 +2467,52 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>2025-08</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
+          <t>2022-02</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D114" t="n">
         <v>9</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>2025-09</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>7</v>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D115" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>2025-10</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>10</v>
+          <t>2022-03</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D116" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="117">
@@ -1941,11 +2521,16 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>2025-11</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>14</v>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D117" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="118">
@@ -1954,11 +2539,16 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>2025-12</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>9</v>
+          <t>2022-04</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D118" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="119">
@@ -1967,11 +2557,16 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>2026-01</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>5</v>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D119" t="n">
+        <v>11</v>
       </c>
     </row>
     <row r="120">
@@ -1980,11 +2575,16 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>2026-02</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>5</v>
+          <t>2022-05</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D120" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="121">
@@ -1993,11 +2593,16 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>2026-03</t>
-        </is>
-      </c>
-      <c r="C121" t="n">
-        <v>14</v>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D121" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="122">
@@ -2006,11 +2611,1456 @@
       </c>
       <c r="B122" t="inlineStr">
         <is>
+          <t>2022-06</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D122" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>121</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D123" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>122</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2022-07</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D124" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>123</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D125" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>124</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2022-08</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D126" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>126</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D127" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>125</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>2022-09</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D128" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>127</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D129" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>128</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2022-10</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D130" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>129</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D131" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>130</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>2022-11</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D132" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>131</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>2022-12</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D133" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>132</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D134" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>133</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>2023-01</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D135" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>134</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D136" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>135</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>2023-02</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D137" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>137</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D138" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>136</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>2023-03</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D139" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>139</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D140" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>138</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>2023-04</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D141" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>140</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D142" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>141</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>2023-05</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D143" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>142</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>2023-06</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D144" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>143</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>2023-07</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D145" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="n">
+        <v>144</v>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D146" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="n">
+        <v>145</v>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>2023-08</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D147" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="n">
+        <v>146</v>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D148" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="n">
+        <v>147</v>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>2023-09</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D149" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="n">
+        <v>148</v>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D150" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="n">
+        <v>149</v>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>2023-10</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D151" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="n">
+        <v>150</v>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>2023-11</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D152" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="n">
+        <v>152</v>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D153" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="n">
+        <v>151</v>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>2023-12</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D154" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="n">
+        <v>153</v>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D155" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="n">
+        <v>154</v>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>2024-01</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D156" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="n">
+        <v>155</v>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>2024-02</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D157" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="n">
+        <v>156</v>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>2024-03</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D158" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="n">
+        <v>157</v>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>2024-04</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D159" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="n">
+        <v>158</v>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>2024-05</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D160" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="n">
+        <v>159</v>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D161" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="n">
+        <v>160</v>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>2024-06</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D162" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="n">
+        <v>161</v>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D163" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="n">
+        <v>162</v>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>2024-07</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D164" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="n">
+        <v>163</v>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>2024-08</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D165" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="n">
+        <v>165</v>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D166" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="n">
+        <v>164</v>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>2024-09</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D167" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="n">
+        <v>166</v>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D168" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="n">
+        <v>167</v>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>2024-10</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D169" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="n">
+        <v>168</v>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>2024-11</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D170" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="n">
+        <v>169</v>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>2024-12</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D171" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="n">
+        <v>170</v>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D172" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="n">
+        <v>171</v>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>2025-01</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D173" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="n">
+        <v>172</v>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D174" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="n">
+        <v>173</v>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2025-02</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="n">
+        <v>174</v>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="n">
+        <v>175</v>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2025-03</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="n">
+        <v>176</v>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>2025-04</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="1" t="n">
+        <v>177</v>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="n">
+        <v>178</v>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="1" t="n">
+        <v>179</v>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2025-06</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="1" t="n">
+        <v>180</v>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>2025-07</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="1" t="n">
+        <v>181</v>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="1" t="n">
+        <v>182</v>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>2025-08</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="n">
+        <v>183</v>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="n">
+        <v>184</v>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>2025-09</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="n">
+        <v>185</v>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="n">
+        <v>186</v>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>2025-10</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="n">
+        <v>188</v>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="n">
+        <v>187</v>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>2025-11</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="1" t="n">
+        <v>189</v>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="n">
+        <v>190</v>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>2025-12</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="n">
+        <v>191</v>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D193" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="n">
+        <v>192</v>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>2026-01</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D194" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="n">
+        <v>193</v>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D195" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="n">
+        <v>194</v>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>2026-02</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D196" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="1" t="n">
+        <v>195</v>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D197" t="n">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="n">
+        <v>196</v>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>2026-03</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D198" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="n">
+        <v>197</v>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
           <t>2026-04</t>
         </is>
       </c>
-      <c r="C122" t="n">
-        <v>12</v>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D199" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="n">
+        <v>198</v>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>2026-04</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D200" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" s="1" t="n">
+        <v>199</v>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D201" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" s="1" t="n">
+        <v>200</v>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>2026-05</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D202" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/data/nuevos_clientes.xlsx
+++ b/data/nuevos_clientes.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D202"/>
+  <dimension ref="A1:D204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1293,7 +1293,7 @@
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B49" t="inlineStr">
         <is>
@@ -1302,16 +1302,16 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B50" t="inlineStr">
         <is>
@@ -1320,11 +1320,11 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51">
@@ -2481,7 +2481,7 @@
     </row>
     <row r="115">
       <c r="A115" s="1" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B115" t="inlineStr">
         <is>
@@ -2490,16 +2490,16 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Salta</t>
+          <t>Buenos Aires</t>
         </is>
       </c>
       <c r="D115" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B116" t="inlineStr">
         <is>
@@ -2508,11 +2508,11 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Buenos Aires</t>
+          <t>Salta</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
     </row>
     <row r="117">
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202">
@@ -4060,6 +4060,42 @@
         </is>
       </c>
       <c r="D202" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" s="1" t="n">
+        <v>201</v>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Buenos Aires</t>
+        </is>
+      </c>
+      <c r="D203" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" s="1" t="n">
+        <v>202</v>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>2026-06</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Salta</t>
+        </is>
+      </c>
+      <c r="D204" t="n">
         <v>1</v>
       </c>
     </row>

--- a/data/nuevos_clientes.xlsx
+++ b/data/nuevos_clientes.xlsx
@@ -4078,7 +4078,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="204">
